--- a/artfynd/A 40520-2025 artfynd.xlsx
+++ b/artfynd/A 40520-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>79608669</v>
+        <v>79608746</v>
       </c>
       <c r="B2" t="n">
-        <v>57073</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,38 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103056</v>
+        <v>1467</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Videsparv</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Emberiza rustica</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Pallas, 1776</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Området kring Nordgrenmyran-Risbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>613582.8626045252</v>
+        <v>613587</v>
       </c>
       <c r="R2" t="n">
-        <v>7186786.951910204</v>
+        <v>7186781</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -752,24 +743,9 @@
           <t>2019-08-20</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-08-20</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>I lämplig häckningsbiotop</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,50 +772,49 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>79608746</v>
+        <v>79608669</v>
       </c>
       <c r="B3" t="n">
-        <v>73698</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58656</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1467</v>
+        <v>103056</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Videsparv</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Emberiza rustica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Pallas, 1776</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Området kring Nordgrenmyran-Risbäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>613586.9287793937</v>
+        <v>613583</v>
       </c>
       <c r="R3" t="n">
-        <v>7186781.129608202</v>
+        <v>7186787</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -869,19 +844,14 @@
           <t>2019-08-20</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-08-20</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>I lämplig häckningsbiotop</t>
         </is>
       </c>
       <c r="AD3" t="b">
